--- a/docs/08_財務・KPI/財務・KPI管理.xlsx
+++ b/docs/08_財務・KPI/財務・KPI管理.xlsx
@@ -13,6 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月次レビュー" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="データ活用ロードマップ" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方ガイド" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1億円逆算ダッシュボード" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="消費者ファネル管理" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,8 +23,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +70,24 @@
       <color rgb="00888888"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002E4057"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00E8740C"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -84,8 +104,26 @@
         <fgColor rgb="003D2200"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E4057"/>
+        <bgColor rgb="002E4057"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8F9FA"/>
+        <bgColor rgb="00F8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8740C"/>
+        <bgColor rgb="00E8740C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -107,11 +145,25 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D5D8DC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D5D8DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5D8DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5D8DC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -136,6 +188,34 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1883,24 +1963,6 @@
           <t>月次請求サマリー（経理部共有用）</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n"/>
-      <c r="C40" s="15" t="n"/>
-      <c r="D40" s="15" t="n"/>
-      <c r="E40" s="15" t="n"/>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
-      <c r="H40" s="15" t="n"/>
-      <c r="I40" s="15" t="n"/>
-      <c r="J40" s="15" t="n"/>
-      <c r="K40" s="15" t="n"/>
-      <c r="L40" s="15" t="n"/>
-      <c r="M40" s="15" t="n"/>
-      <c r="N40" s="15" t="n"/>
-      <c r="O40" s="15" t="n"/>
-      <c r="P40" s="15" t="n"/>
-      <c r="Q40" s="15" t="n"/>
-      <c r="R40" s="15" t="n"/>
-      <c r="S40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -3780,4 +3842,1361 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>ぺいほーむ 1億円逆算ダッシュボード</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>年間目標分解</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>収益源</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>単価</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>月間目標件数</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>年間目標件数</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>年間売上目標</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>構成比</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>実績累計</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>達成率</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>資料請求</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>1,800</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>1,440万</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="19">
+        <f>IF(G5="","",G5/E5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>見学会来場</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="D6" s="20" t="n">
+        <v>840</v>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>6,720万</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20">
+        <f>IF(G6="","",G6/E6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>成約報酬</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>1,000,000</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>3,000万</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="n"/>
+      <c r="H7" s="19">
+        <f>IF(G7="","",G7/E7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>掲載料</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>40,000/月</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>30社</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>1,440万</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20">
+        <f>IF(G8="","",G8/E8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>12,600万</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G9" s="21">
+        <f>SUM(G5:G8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="21">
+        <f>IF(G9=0,"",G9/126000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>月次売上トラッキング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>資料請求件数</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>資料請求売上</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>見学会件数</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>見学会売上</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>成約件数</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>成約報酬</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>掲載料</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>撮影費</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>マーケ支援</t>
+        </is>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>月間合計</t>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>累計</t>
+        </is>
+      </c>
+      <c r="M13" s="18" t="inlineStr">
+        <is>
+          <t>1億円達成率</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="19">
+        <f>B14*8000</f>
+        <v/>
+      </c>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19">
+        <f>D14*80000</f>
+        <v/>
+      </c>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19">
+        <f>F14*1000000</f>
+        <v/>
+      </c>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
+      <c r="J14" s="19" t="n"/>
+      <c r="K14" s="19">
+        <f>C14+E14+G14+H14+I14+J14</f>
+        <v/>
+      </c>
+      <c r="L14" s="19">
+        <f>K14</f>
+        <v/>
+      </c>
+      <c r="M14" s="22">
+        <f>L14/100000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20">
+        <f>B15*8000</f>
+        <v/>
+      </c>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20">
+        <f>D15*80000</f>
+        <v/>
+      </c>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="20">
+        <f>F15*1000000</f>
+        <v/>
+      </c>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="20" t="n"/>
+      <c r="J15" s="20" t="n"/>
+      <c r="K15" s="20">
+        <f>C15+E15+G15+H15+I15+J15</f>
+        <v/>
+      </c>
+      <c r="L15" s="20">
+        <f>L14+K15</f>
+        <v/>
+      </c>
+      <c r="M15" s="23">
+        <f>L15/100000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="19">
+        <f>B16*8000</f>
+        <v/>
+      </c>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19">
+        <f>D16*80000</f>
+        <v/>
+      </c>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="19">
+        <f>F16*1000000</f>
+        <v/>
+      </c>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="19" t="n"/>
+      <c r="J16" s="19" t="n"/>
+      <c r="K16" s="19">
+        <f>C16+E16+G16+H16+I16+J16</f>
+        <v/>
+      </c>
+      <c r="L16" s="19">
+        <f>L15+K16</f>
+        <v/>
+      </c>
+      <c r="M16" s="22">
+        <f>L16/100000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20">
+        <f>B17*8000</f>
+        <v/>
+      </c>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="20">
+        <f>D17*80000</f>
+        <v/>
+      </c>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="20">
+        <f>F17*1000000</f>
+        <v/>
+      </c>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="20" t="n"/>
+      <c r="J17" s="20" t="n"/>
+      <c r="K17" s="20">
+        <f>C17+E17+G17+H17+I17+J17</f>
+        <v/>
+      </c>
+      <c r="L17" s="20">
+        <f>L16+K17</f>
+        <v/>
+      </c>
+      <c r="M17" s="23">
+        <f>L17/100000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19">
+        <f>B18*8000</f>
+        <v/>
+      </c>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19">
+        <f>D18*80000</f>
+        <v/>
+      </c>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="19">
+        <f>F18*1000000</f>
+        <v/>
+      </c>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="19">
+        <f>C18+E18+G18+H18+I18+J18</f>
+        <v/>
+      </c>
+      <c r="L18" s="19">
+        <f>L17+K18</f>
+        <v/>
+      </c>
+      <c r="M18" s="22">
+        <f>L18/100000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="20">
+        <f>B19*8000</f>
+        <v/>
+      </c>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="20">
+        <f>D19*80000</f>
+        <v/>
+      </c>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="20">
+        <f>F19*1000000</f>
+        <v/>
+      </c>
+      <c r="H19" s="20" t="n"/>
+      <c r="I19" s="20" t="n"/>
+      <c r="J19" s="20" t="n"/>
+      <c r="K19" s="20">
+        <f>C19+E19+G19+H19+I19+J19</f>
+        <v/>
+      </c>
+      <c r="L19" s="20">
+        <f>L18+K19</f>
+        <v/>
+      </c>
+      <c r="M19" s="23">
+        <f>L19/100000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n"/>
+      <c r="C20" s="19">
+        <f>B20*8000</f>
+        <v/>
+      </c>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19">
+        <f>D20*80000</f>
+        <v/>
+      </c>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19">
+        <f>F20*1000000</f>
+        <v/>
+      </c>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="19" t="n"/>
+      <c r="J20" s="19" t="n"/>
+      <c r="K20" s="19">
+        <f>C20+E20+G20+H20+I20+J20</f>
+        <v/>
+      </c>
+      <c r="L20" s="19">
+        <f>L19+K20</f>
+        <v/>
+      </c>
+      <c r="M20" s="22">
+        <f>L20/100000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20">
+        <f>B21*8000</f>
+        <v/>
+      </c>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="20">
+        <f>D21*80000</f>
+        <v/>
+      </c>
+      <c r="F21" s="20" t="n"/>
+      <c r="G21" s="20">
+        <f>F21*1000000</f>
+        <v/>
+      </c>
+      <c r="H21" s="20" t="n"/>
+      <c r="I21" s="20" t="n"/>
+      <c r="J21" s="20" t="n"/>
+      <c r="K21" s="20">
+        <f>C21+E21+G21+H21+I21+J21</f>
+        <v/>
+      </c>
+      <c r="L21" s="20">
+        <f>L20+K21</f>
+        <v/>
+      </c>
+      <c r="M21" s="23">
+        <f>L21/100000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="19">
+        <f>B22*8000</f>
+        <v/>
+      </c>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19">
+        <f>D22*80000</f>
+        <v/>
+      </c>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19">
+        <f>F22*1000000</f>
+        <v/>
+      </c>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="19" t="n"/>
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="19">
+        <f>C22+E22+G22+H22+I22+J22</f>
+        <v/>
+      </c>
+      <c r="L22" s="19">
+        <f>L21+K22</f>
+        <v/>
+      </c>
+      <c r="M22" s="22">
+        <f>L22/100000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="20">
+        <f>B23*8000</f>
+        <v/>
+      </c>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="20">
+        <f>D23*80000</f>
+        <v/>
+      </c>
+      <c r="F23" s="20" t="n"/>
+      <c r="G23" s="20">
+        <f>F23*1000000</f>
+        <v/>
+      </c>
+      <c r="H23" s="20" t="n"/>
+      <c r="I23" s="20" t="n"/>
+      <c r="J23" s="20" t="n"/>
+      <c r="K23" s="20">
+        <f>C23+E23+G23+H23+I23+J23</f>
+        <v/>
+      </c>
+      <c r="L23" s="20">
+        <f>L22+K23</f>
+        <v/>
+      </c>
+      <c r="M23" s="23">
+        <f>L23/100000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="19">
+        <f>B24*8000</f>
+        <v/>
+      </c>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19">
+        <f>D24*80000</f>
+        <v/>
+      </c>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="19">
+        <f>F24*1000000</f>
+        <v/>
+      </c>
+      <c r="H24" s="19" t="n"/>
+      <c r="I24" s="19" t="n"/>
+      <c r="J24" s="19" t="n"/>
+      <c r="K24" s="19">
+        <f>C24+E24+G24+H24+I24+J24</f>
+        <v/>
+      </c>
+      <c r="L24" s="19">
+        <f>L23+K24</f>
+        <v/>
+      </c>
+      <c r="M24" s="22">
+        <f>L24/100000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="20">
+        <f>B25*8000</f>
+        <v/>
+      </c>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="20">
+        <f>D25*80000</f>
+        <v/>
+      </c>
+      <c r="F25" s="20" t="n"/>
+      <c r="G25" s="20">
+        <f>F25*1000000</f>
+        <v/>
+      </c>
+      <c r="H25" s="20" t="n"/>
+      <c r="I25" s="20" t="n"/>
+      <c r="J25" s="20" t="n"/>
+      <c r="K25" s="20">
+        <f>C25+E25+G25+H25+I25+J25</f>
+        <v/>
+      </c>
+      <c r="L25" s="20">
+        <f>L24+K25</f>
+        <v/>
+      </c>
+      <c r="M25" s="23">
+        <f>L25/100000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>1社あたりの月間目標</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>50社平均</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>上位15社平均</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>その他35社平均</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>資料請求</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>3件</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>6件</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>1.7件</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>見学会来場</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>1.4件</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>3件</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>0.7件</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>成約</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>0.05棟</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>0.13棟</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>PF訪問者</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>資料請求</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>転換率</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>見学会予約</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>転換率</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t>商談</t>
+        </is>
+      </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t>転換率</t>
+        </is>
+      </c>
+      <c r="I1" s="18" t="inlineStr">
+        <is>
+          <t>成約</t>
+        </is>
+      </c>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>転換率</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
+          <t>成約報酬</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="22">
+        <f>IF(B2=0,"",C2/B2)</f>
+        <v/>
+      </c>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="22">
+        <f>IF(B2=0,"",E2/B2)</f>
+        <v/>
+      </c>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="22">
+        <f>IF(B2=0,"",G2/B2)</f>
+        <v/>
+      </c>
+      <c r="I2" s="19" t="n"/>
+      <c r="J2" s="22">
+        <f>IF(B2=0,"",I2/B2)</f>
+        <v/>
+      </c>
+      <c r="K2" s="24">
+        <f>I2*1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="23">
+        <f>IF(B3=0,"",C3/B3)</f>
+        <v/>
+      </c>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="23">
+        <f>IF(B3=0,"",E3/B3)</f>
+        <v/>
+      </c>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="23">
+        <f>IF(B3=0,"",G3/B3)</f>
+        <v/>
+      </c>
+      <c r="I3" s="20" t="n"/>
+      <c r="J3" s="23">
+        <f>IF(B3=0,"",I3/B3)</f>
+        <v/>
+      </c>
+      <c r="K3" s="25">
+        <f>I3*1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="22">
+        <f>IF(B4=0,"",C4/B4)</f>
+        <v/>
+      </c>
+      <c r="E4" s="19" t="n"/>
+      <c r="F4" s="22">
+        <f>IF(B4=0,"",E4/B4)</f>
+        <v/>
+      </c>
+      <c r="G4" s="19" t="n"/>
+      <c r="H4" s="22">
+        <f>IF(B4=0,"",G4/B4)</f>
+        <v/>
+      </c>
+      <c r="I4" s="19" t="n"/>
+      <c r="J4" s="22">
+        <f>IF(B4=0,"",I4/B4)</f>
+        <v/>
+      </c>
+      <c r="K4" s="24">
+        <f>I4*1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="23">
+        <f>IF(B5=0,"",C5/B5)</f>
+        <v/>
+      </c>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="23">
+        <f>IF(B5=0,"",E5/B5)</f>
+        <v/>
+      </c>
+      <c r="G5" s="20" t="n"/>
+      <c r="H5" s="23">
+        <f>IF(B5=0,"",G5/B5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="20" t="n"/>
+      <c r="J5" s="23">
+        <f>IF(B5=0,"",I5/B5)</f>
+        <v/>
+      </c>
+      <c r="K5" s="25">
+        <f>I5*1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="n"/>
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="22">
+        <f>IF(B6=0,"",C6/B6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="22">
+        <f>IF(B6=0,"",E6/B6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="19" t="n"/>
+      <c r="H6" s="22">
+        <f>IF(B6=0,"",G6/B6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="19" t="n"/>
+      <c r="J6" s="22">
+        <f>IF(B6=0,"",I6/B6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="24">
+        <f>I6*1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="23">
+        <f>IF(B7=0,"",C7/B7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="23">
+        <f>IF(B7=0,"",E7/B7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="23">
+        <f>IF(B7=0,"",G7/B7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="20" t="n"/>
+      <c r="J7" s="23">
+        <f>IF(B7=0,"",I7/B7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="25">
+        <f>I7*1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="n"/>
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="22">
+        <f>IF(B8=0,"",C8/B8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="22">
+        <f>IF(B8=0,"",E8/B8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="19" t="n"/>
+      <c r="H8" s="22">
+        <f>IF(B8=0,"",G8/B8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="22">
+        <f>IF(B8=0,"",I8/B8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="24">
+        <f>I8*1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="23">
+        <f>IF(B9=0,"",C9/B9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="23">
+        <f>IF(B9=0,"",E9/B9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="23">
+        <f>IF(B9=0,"",G9/B9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="20" t="n"/>
+      <c r="J9" s="23">
+        <f>IF(B9=0,"",I9/B9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="25">
+        <f>I9*1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="22">
+        <f>IF(B10=0,"",C10/B10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="22">
+        <f>IF(B10=0,"",E10/B10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="22">
+        <f>IF(B10=0,"",G10/B10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="19" t="n"/>
+      <c r="J10" s="22">
+        <f>IF(B10=0,"",I10/B10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="24">
+        <f>I10*1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="23">
+        <f>IF(B11=0,"",C11/B11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="23">
+        <f>IF(B11=0,"",E11/B11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="23">
+        <f>IF(B11=0,"",G11/B11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="20" t="n"/>
+      <c r="J11" s="23">
+        <f>IF(B11=0,"",I11/B11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="25">
+        <f>I11*1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="22">
+        <f>IF(B12=0,"",C12/B12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="22">
+        <f>IF(B12=0,"",E12/B12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="22">
+        <f>IF(B12=0,"",G12/B12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="22">
+        <f>IF(B12=0,"",I12/B12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="24">
+        <f>I12*1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="23">
+        <f>IF(B13=0,"",C13/B13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="23">
+        <f>IF(B13=0,"",E13/B13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="23">
+        <f>IF(B13=0,"",G13/B13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="20" t="n"/>
+      <c r="J13" s="23">
+        <f>IF(B13=0,"",I13/B13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="25">
+        <f>I13*1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/08_財務・KPI/財務・KPI管理.xlsx
+++ b/docs/08_財務・KPI/財務・KPI管理.xlsx
@@ -26,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,8 +86,13 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -120,6 +125,21 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8740C"/>
         <bgColor rgb="00E8740C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E4057"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8F9FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -163,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -216,6 +236,32 @@
     <xf numFmtId="3" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="10" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="11" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -582,19 +628,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S48"/>
+  <dimension ref="A1:S65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="5" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -2263,9 +2309,448 @@
       </c>
       <c r="I48" s="3" t="n"/>
     </row>
+    <row r="51">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>【成果報酬 月次集計】</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="B52" s="27" t="inlineStr">
+        <is>
+          <t>資料請求件数</t>
+        </is>
+      </c>
+      <c r="C52" s="27" t="inlineStr">
+        <is>
+          <t>単価</t>
+        </is>
+      </c>
+      <c r="D52" s="27" t="inlineStr">
+        <is>
+          <t>資料請求売上</t>
+        </is>
+      </c>
+      <c r="E52" s="27" t="inlineStr">
+        <is>
+          <t>見学会来場件数</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="inlineStr">
+        <is>
+          <t>単価</t>
+        </is>
+      </c>
+      <c r="G52" s="27" t="inlineStr">
+        <is>
+          <t>見学会売上</t>
+        </is>
+      </c>
+      <c r="H52" s="27" t="inlineStr">
+        <is>
+          <t>成約件数</t>
+        </is>
+      </c>
+      <c r="I52" s="27" t="inlineStr">
+        <is>
+          <t>成約報酬額</t>
+        </is>
+      </c>
+      <c r="J52" s="27" t="inlineStr">
+        <is>
+          <t>月間成果報酬合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="28" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="B53" s="29" t="n"/>
+      <c r="C53" s="30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D53" s="31">
+        <f>B53*C53</f>
+        <v/>
+      </c>
+      <c r="E53" s="29" t="n"/>
+      <c r="F53" s="30" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G53" s="31">
+        <f>E53*F53</f>
+        <v/>
+      </c>
+      <c r="H53" s="29" t="n"/>
+      <c r="I53" s="29" t="n"/>
+      <c r="J53" s="32">
+        <f>D53+G53+I53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="33" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="B54" s="34" t="n"/>
+      <c r="C54" s="35" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D54" s="36">
+        <f>B54*C54</f>
+        <v/>
+      </c>
+      <c r="E54" s="34" t="n"/>
+      <c r="F54" s="35" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G54" s="36">
+        <f>E54*F54</f>
+        <v/>
+      </c>
+      <c r="H54" s="34" t="n"/>
+      <c r="I54" s="34" t="n"/>
+      <c r="J54" s="37">
+        <f>D54+G54+I54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="28" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="B55" s="29" t="n"/>
+      <c r="C55" s="30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D55" s="31">
+        <f>B55*C55</f>
+        <v/>
+      </c>
+      <c r="E55" s="29" t="n"/>
+      <c r="F55" s="30" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G55" s="31">
+        <f>E55*F55</f>
+        <v/>
+      </c>
+      <c r="H55" s="29" t="n"/>
+      <c r="I55" s="29" t="n"/>
+      <c r="J55" s="32">
+        <f>D55+G55+I55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="33" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="B56" s="34" t="n"/>
+      <c r="C56" s="35" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D56" s="36">
+        <f>B56*C56</f>
+        <v/>
+      </c>
+      <c r="E56" s="34" t="n"/>
+      <c r="F56" s="35" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G56" s="36">
+        <f>E56*F56</f>
+        <v/>
+      </c>
+      <c r="H56" s="34" t="n"/>
+      <c r="I56" s="34" t="n"/>
+      <c r="J56" s="37">
+        <f>D56+G56+I56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="28" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="B57" s="29" t="n"/>
+      <c r="C57" s="30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D57" s="31">
+        <f>B57*C57</f>
+        <v/>
+      </c>
+      <c r="E57" s="29" t="n"/>
+      <c r="F57" s="30" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G57" s="31">
+        <f>E57*F57</f>
+        <v/>
+      </c>
+      <c r="H57" s="29" t="n"/>
+      <c r="I57" s="29" t="n"/>
+      <c r="J57" s="32">
+        <f>D57+G57+I57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="33" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="B58" s="34" t="n"/>
+      <c r="C58" s="35" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D58" s="36">
+        <f>B58*C58</f>
+        <v/>
+      </c>
+      <c r="E58" s="34" t="n"/>
+      <c r="F58" s="35" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G58" s="36">
+        <f>E58*F58</f>
+        <v/>
+      </c>
+      <c r="H58" s="34" t="n"/>
+      <c r="I58" s="34" t="n"/>
+      <c r="J58" s="37">
+        <f>D58+G58+I58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="B59" s="29" t="n"/>
+      <c r="C59" s="30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D59" s="31">
+        <f>B59*C59</f>
+        <v/>
+      </c>
+      <c r="E59" s="29" t="n"/>
+      <c r="F59" s="30" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G59" s="31">
+        <f>E59*F59</f>
+        <v/>
+      </c>
+      <c r="H59" s="29" t="n"/>
+      <c r="I59" s="29" t="n"/>
+      <c r="J59" s="32">
+        <f>D59+G59+I59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="33" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="B60" s="34" t="n"/>
+      <c r="C60" s="35" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D60" s="36">
+        <f>B60*C60</f>
+        <v/>
+      </c>
+      <c r="E60" s="34" t="n"/>
+      <c r="F60" s="35" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G60" s="36">
+        <f>E60*F60</f>
+        <v/>
+      </c>
+      <c r="H60" s="34" t="n"/>
+      <c r="I60" s="34" t="n"/>
+      <c r="J60" s="37">
+        <f>D60+G60+I60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="28" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="B61" s="29" t="n"/>
+      <c r="C61" s="30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D61" s="31">
+        <f>B61*C61</f>
+        <v/>
+      </c>
+      <c r="E61" s="29" t="n"/>
+      <c r="F61" s="30" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G61" s="31">
+        <f>E61*F61</f>
+        <v/>
+      </c>
+      <c r="H61" s="29" t="n"/>
+      <c r="I61" s="29" t="n"/>
+      <c r="J61" s="32">
+        <f>D61+G61+I61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="33" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="B62" s="34" t="n"/>
+      <c r="C62" s="35" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D62" s="36">
+        <f>B62*C62</f>
+        <v/>
+      </c>
+      <c r="E62" s="34" t="n"/>
+      <c r="F62" s="35" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G62" s="36">
+        <f>E62*F62</f>
+        <v/>
+      </c>
+      <c r="H62" s="34" t="n"/>
+      <c r="I62" s="34" t="n"/>
+      <c r="J62" s="37">
+        <f>D62+G62+I62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="28" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="B63" s="29" t="n"/>
+      <c r="C63" s="30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D63" s="31">
+        <f>B63*C63</f>
+        <v/>
+      </c>
+      <c r="E63" s="29" t="n"/>
+      <c r="F63" s="30" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G63" s="31">
+        <f>E63*F63</f>
+        <v/>
+      </c>
+      <c r="H63" s="29" t="n"/>
+      <c r="I63" s="29" t="n"/>
+      <c r="J63" s="32">
+        <f>D63+G63+I63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="33" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="B64" s="34" t="n"/>
+      <c r="C64" s="35" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D64" s="36">
+        <f>B64*C64</f>
+        <v/>
+      </c>
+      <c r="E64" s="34" t="n"/>
+      <c r="F64" s="35" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G64" s="36">
+        <f>E64*F64</f>
+        <v/>
+      </c>
+      <c r="H64" s="34" t="n"/>
+      <c r="I64" s="34" t="n"/>
+      <c r="J64" s="37">
+        <f>D64+G64+I64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="38" t="inlineStr">
+        <is>
+          <t>年間合計</t>
+        </is>
+      </c>
+      <c r="B65" s="39">
+        <f>SUM(B53:B64)</f>
+        <v/>
+      </c>
+      <c r="D65" s="39">
+        <f>SUM(D53:D64)</f>
+        <v/>
+      </c>
+      <c r="E65" s="39">
+        <f>SUM(E53:E64)</f>
+        <v/>
+      </c>
+      <c r="G65" s="39">
+        <f>SUM(G53:G64)</f>
+        <v/>
+      </c>
+      <c r="I65" s="39">
+        <f>SUM(I53:I64)</f>
+        <v/>
+      </c>
+      <c r="J65" s="39">
+        <f>SUM(J53:J64)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A40:S40"/>
+    <mergeCell ref="A51:J51"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -3850,7 +4335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3875,7 +4360,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
@@ -4103,8 +4587,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
@@ -4623,8 +5105,6 @@
         <v/>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
@@ -4720,7 +5200,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A28:D28"/>
@@ -4738,7 +5217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5195,7 +5674,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
